--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_63_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_63_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9001</v>
+        <v>6.6038</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9341</v>
+        <v>4.537</v>
       </c>
       <c r="F2" t="n">
-        <v>1.966</v>
+        <v>2.0668</v>
       </c>
       <c r="G2" t="n">
         <v>5.5</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9361</v>
+        <v>0.6398</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5272</v>
+        <v>0.13</v>
       </c>
       <c r="U2" t="n">
-        <v>0.409</v>
+        <v>0.5098</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9275</v>
+        <v>1.879</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4893</v>
+        <v>1.9993</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4382</v>
+        <v>-0.1203</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0166</v>
+        <v>1.5203</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.2078</v>
+        <v>-0.156</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1912</v>
+        <v>1.6763</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3371</v>
+        <v>1.7634</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4278</v>
+        <v>0.0336</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0907</v>
+        <v>1.7298</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6795</v>
+        <v>-0.2431</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>-0.1896</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1005</v>
+        <v>-0.0535</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8719</v>
+        <v>0.1267</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5375</v>
+        <v>0.2359</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3343</v>
+        <v>-0.1092</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7439</v>
+        <v>1.506</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7634</v>
+        <v>-0.4168</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0195</v>
+        <v>1.9228</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5203</v>
+        <v>-0.5886</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.156</v>
+        <v>-0.9233</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6763</v>
+        <v>0.3348</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7634</v>
+        <v>0.366</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0336</v>
+        <v>0.182</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7298</v>
+        <v>0.184</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2431</v>
+        <v>-0.9546</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1896</v>
+        <v>-1.1053</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0535</v>
+        <v>0.1507</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0083</v>
+        <v>0.8806</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.3227</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0083</v>
+        <v>0.5579</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7105</v>
+        <v>0.9234</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2123</v>
+        <v>-0.6156</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9228</v>
+        <v>1.539</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5886</v>
+        <v>-1.0166</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9233</v>
+        <v>-2.2078</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3348</v>
+        <v>1.1912</v>
       </c>
       <c r="J5" t="n">
-        <v>0.366</v>
+        <v>-0.3371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.182</v>
+        <v>-1.4278</v>
       </c>
       <c r="L5" t="n">
-        <v>0.184</v>
+        <v>1.0907</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9546</v>
+        <v>-0.6795</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1053</v>
+        <v>-0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1507</v>
+        <v>0.1005</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0851</v>
+        <v>0.8678</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5272</v>
+        <v>0.4327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5579</v>
+        <v>0.4351</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3413</v>
+        <v>0.8367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2072</v>
+        <v>-1.3097</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5485</v>
+        <v>2.1465</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2048</v>
+        <v>-0.7047</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006</v>
+        <v>0.6338</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2108</v>
+        <v>-1.3385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0168</v>
+        <v>0.5756</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0168</v>
+        <v>2.2756</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.7001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2216</v>
+        <v>-1.2803</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0108</v>
+        <v>-1.6418</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2108</v>
+        <v>0.3615</v>
       </c>
       <c r="P6" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5414</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>-0.1019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3062</v>
+        <v>0.6434</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1209</v>
+        <v>0.5078</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.328</v>
+        <v>0.0601</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4489</v>
+        <v>0.4477</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7047</v>
+        <v>-0.2048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6338</v>
+        <v>0.006</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3385</v>
+        <v>-0.2108</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5756</v>
+        <v>0.0168</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2756</v>
+        <v>0.0168</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7001</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2803</v>
+        <v>-0.2216</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6418</v>
+        <v>-0.0108</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3615</v>
+        <v>-0.2108</v>
       </c>
       <c r="P7" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1744</v>
+        <v>0.2486</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1202</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9458</v>
+        <v>0.2054</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3208</v>
+        <v>0.0336</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3282</v>
+        <v>-1.5104</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0075</v>
+        <v>1.544</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0598</v>
+        <v>3.7371</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6722</v>
+        <v>1.7395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6124000000000001</v>
+        <v>1.9976</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0907</v>
+        <v>4.2095</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0539</v>
+        <v>3.0452</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>1.1643</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1505</v>
+        <v>-0.4724</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7261</v>
+        <v>-1.3057</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5756</v>
+        <v>0.8333</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-5.7988</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1308</v>
+        <v>0.2396</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9006</v>
+        <v>0.0788</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2302</v>
+        <v>0.1608</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7499</v>
+        <v>-0.5999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5038</v>
+        <v>-1.1185</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7539</v>
+        <v>0.5187</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5822000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4872</v>
+        <v>-0.3372</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.4362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3343</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1356</v>
+        <v>-1.0643</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4107</v>
+        <v>-2.0045</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2752</v>
+        <v>0.9402</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7371</v>
+        <v>-0.0598</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7395</v>
+        <v>-0.6722</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9976</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2095</v>
+        <v>0.0907</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0452</v>
+        <v>0.0539</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1643</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4724</v>
+        <v>-0.1505</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3057</v>
+        <v>-0.7261</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8333</v>
+        <v>0.5756</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.9432</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.7988</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9296</v>
+        <v>0.3872</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>0.2243</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1081</v>
+        <v>0.163</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0533</v>
+        <v>-2.659</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4106</v>
+        <v>-2.2179</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6427</v>
+        <v>-0.4411</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7909</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8681</v>
+        <v>-0.4738</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9304</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5591</v>
+        <v>-3.9214</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.989</v>
+        <v>-4.4858</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4299</v>
+        <v>0.5643</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9321</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7714</v>
+        <v>-0.1338</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4481</v>
+        <v>0.0551</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9255</v>
+        <v>4.045699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.202999999999999</v>
+        <v>-7.082800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>11.1287</v>
+        <v>11.1286</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8777</v>
+        <v>4.877699999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-3.2532</v>
@@ -1441,7 +1441,7 @@
         <v>8.130999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>9.563099999999999</v>
+        <v>9.563100000000002</v>
       </c>
       <c r="K13" t="n">
         <v>4.277299999999999</v>
@@ -1459,7 +1459,7 @@
         <v>2.8451</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.639</v>
+        <v>-4.638999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.8756</v>
@@ -1468,13 +1468,13 @@
         <v>16.2366</v>
       </c>
       <c r="S13" t="n">
-        <v>1.867</v>
+        <v>2.9869</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3908999999999998</v>
+        <v>0.7292</v>
       </c>
       <c r="U13" t="n">
-        <v>2.258</v>
+        <v>2.2581</v>
       </c>
       <c r="V13" t="n">
         <v>0.8197</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9162</v>
+        <v>2.9676</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2718</v>
+        <v>2.6257</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6444</v>
+        <v>0.3419</v>
       </c>
       <c r="G14" t="n">
         <v>3.6212</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4731</v>
+        <v>-0.4217</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4977</v>
+        <v>0.1953</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6059</v>
+        <v>2.5216</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0595</v>
+        <v>2.9415</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4535</v>
+        <v>-0.4199</v>
       </c>
       <c r="G15" t="n">
         <v>1.3412</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3369</v>
+        <v>0.2526</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8808</v>
+        <v>0.7793</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5634</v>
+        <v>0.3275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3175</v>
+        <v>0.4519</v>
       </c>
       <c r="G16" t="n">
         <v>0.1463</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5026</v>
+        <v>0.4011</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0474</v>
+        <v>-0.1885</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4551</v>
+        <v>0.5895</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3278</v>
+        <v>0.3628</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.6087</v>
+        <v>-3.0189</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2809</v>
+        <v>3.3818</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6269</v>
@@ -1780,13 +1780,13 @@
         <v>3.2473</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3245</v>
+        <v>-0.6339</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.955</v>
+        <v>-0.3653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3694</v>
+        <v>-0.2686</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6032</v>
+        <v>-0.659</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0634</v>
+        <v>-0.8818</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4602</v>
+        <v>0.2228</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.134</v>
+        <v>-1.3882</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.287</v>
+        <v>0.4287</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.847</v>
+        <v>-1.8169</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4466</v>
+        <v>-0.8269</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.339</v>
+        <v>0.6722</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1077</v>
+        <v>-1.4991</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6874</v>
+        <v>-0.5613</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.2435</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3178</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2473</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4432</v>
+        <v>-0.1986</v>
       </c>
       <c r="T18" t="n">
-        <v>0.543</v>
+        <v>-0.0549</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0997</v>
+        <v>-0.1436</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0965</v>
+        <v>-0.8308</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1177</v>
+        <v>-0.8238</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0212</v>
+        <v>-0.007</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3882</v>
+        <v>-0.482</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4287</v>
+        <v>0.1069</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8169</v>
+        <v>-0.5889</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8269</v>
+        <v>1.6449</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6722</v>
+        <v>1.1798</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4991</v>
+        <v>0.465</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5613</v>
+        <v>-2.1269</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2435</v>
+        <v>-1.073</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3178</v>
+        <v>-1.0539</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6361</v>
+        <v>-0.1169</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2908</v>
+        <v>-0.1491</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3453</v>
+        <v>0.0323</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.239</v>
+        <v>-0.8763</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1581</v>
+        <v>-2.3504</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0809</v>
+        <v>1.4741</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.14</v>
+        <v>1.1163</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1994</v>
+        <v>2.0765</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3395</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1704</v>
+        <v>2.8465</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9579</v>
+        <v>2.6993</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1283</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9696</v>
+        <v>-1.7302</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7584</v>
+        <v>-0.6227</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2112</v>
+        <v>-1.1074</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8556</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0154</v>
+        <v>3.2473</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1176</v>
+        <v>-0.3174</v>
       </c>
       <c r="T20" t="n">
-        <v>1.172</v>
+        <v>-0.5579</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0545</v>
+        <v>0.2405</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2473</v>
+        <v>-1.3953</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8223</v>
+        <v>-2.8891</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5749</v>
+        <v>1.4938</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1163</v>
+        <v>-3.134</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0765</v>
+        <v>-1.287</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-1.847</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8465</v>
+        <v>-1.4466</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6993</v>
+        <v>-0.339</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1472</v>
+        <v>-1.1077</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7302</v>
+        <v>-1.6874</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6227</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1074</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
         <v>3.2473</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6884</v>
+        <v>-0.3488</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0297</v>
+        <v>-0.2827</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3413</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4542</v>
+        <v>-2.553</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4136</v>
+        <v>-2.3376</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0406</v>
+        <v>-0.2154</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.482</v>
+        <v>-3.14</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1069</v>
+        <v>0.1994</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5889</v>
+        <v>-3.3395</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6449</v>
+        <v>-1.1704</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1798</v>
+        <v>0.9579</v>
       </c>
       <c r="L22" t="n">
-        <v>0.465</v>
+        <v>-2.1283</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1269</v>
+        <v>-1.9696</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.073</v>
+        <v>-0.7584</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0539</v>
+        <v>-1.2112</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7402</v>
+        <v>-0.1964</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7389</v>
+        <v>-0.0075</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0013</v>
+        <v>-0.1889</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3604</v>
+        <v>-3.2424</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8396</v>
+        <v>-4.7217</v>
       </c>
       <c r="F23" t="n">
         <v>1.4793</v>
@@ -2248,10 +2248,10 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.405</v>
+        <v>-0.2871</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1063</v>
@@ -2284,10 +2284,10 @@
         <v>-2.9255</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.1287</v>
+        <v>-11.1286</v>
       </c>
       <c r="F24" t="n">
-        <v>8.203399999999998</v>
+        <v>8.2033</v>
       </c>
       <c r="G24" t="n">
         <v>-4.877800000000001</v>
@@ -2299,13 +2299,13 @@
         <v>-8.131</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6855</v>
+        <v>4.685500000000001</v>
       </c>
       <c r="K24" t="n">
         <v>7.530599999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.845299999999999</v>
+        <v>-2.8453</v>
       </c>
       <c r="M24" t="n">
         <v>-9.5632</v>
@@ -2326,13 +2326,13 @@
         <v>20.8757</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.867</v>
+        <v>-1.8671</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.258</v>
+        <v>-2.2581</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3909999999999999</v>
+        <v>0.3910999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8197000000000001</v>
